--- a/Rodovias/modelos_rodovias/floriano_rodrigues_pinheiro_km_26_pindamonhangaba_sp_rf_regimes/predicoes_teste.xlsx
+++ b/Rodovias/modelos_rodovias/floriano_rodrigues_pinheiro_km_26_pindamonhangaba_sp_rf_regimes/predicoes_teste.xlsx
@@ -1206,7 +1206,7 @@
         <v>7670</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1878362049444368</v>
+        <v>0.1878362049444367</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
@@ -1435,7 +1435,7 @@
         <v>7800</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.1765224845074773</v>
+        <v>0.1765224845074772</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
         <v>8775</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.2543448809805853</v>
+        <v>0.2543448809805852</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
         <v>10586</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.346331901134811</v>
+        <v>0.3463319011348111</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>10112</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.2835339525965221</v>
+        <v>0.283533952596522</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>10902</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.3307986253456405</v>
+        <v>0.3307986253456406</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
         <v>12087</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.3518554439297059</v>
+        <v>0.351855443929706</v>
       </c>
       <c r="BN17" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>10981</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.3108895090262086</v>
+        <v>0.3108895090262087</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
         <v>8300</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.4081193437852536</v>
+        <v>0.4081193437852535</v>
       </c>
       <c r="BN25" t="n">
         <v>0</v>
@@ -7389,7 +7389,7 @@
         <v>10340</v>
       </c>
       <c r="BM30" t="n">
-        <v>0.2841525304562767</v>
+        <v>0.2841525304562768</v>
       </c>
       <c r="BN30" t="n">
         <v>0</v>
@@ -10137,7 +10137,7 @@
         <v>6460</v>
       </c>
       <c r="BM42" t="n">
-        <v>0.5438589918395282</v>
+        <v>0.5438589918395283</v>
       </c>
       <c r="BN42" t="n">
         <v>1</v>
@@ -10595,7 +10595,7 @@
         <v>7980</v>
       </c>
       <c r="BM44" t="n">
-        <v>0.3162672626947003</v>
+        <v>0.3162672626947002</v>
       </c>
       <c r="BN44" t="n">
         <v>0</v>
@@ -12198,7 +12198,7 @@
         <v>6014</v>
       </c>
       <c r="BM51" t="n">
-        <v>0.2856530899840041</v>
+        <v>0.285653089984004</v>
       </c>
       <c r="BN51" t="n">
         <v>0</v>
@@ -13572,7 +13572,7 @@
         <v>1666</v>
       </c>
       <c r="BM57" t="n">
-        <v>0.4264789262029754</v>
+        <v>0.4264789262029755</v>
       </c>
       <c r="BN57" t="n">
         <v>0</v>
@@ -14259,7 +14259,7 @@
         <v>2156</v>
       </c>
       <c r="BM60" t="n">
-        <v>0.4999345621615691</v>
+        <v>0.499934562161569</v>
       </c>
       <c r="BN60" t="n">
         <v>0</v>
@@ -16256,7 +16256,7 @@
         <v>4655</v>
       </c>
       <c r="BM69" t="n">
-        <v>0.6121966455859125</v>
+        <v>0.6121966455859124</v>
       </c>
       <c r="BN69" t="n">
         <v>1</v>
@@ -17582,7 +17582,7 @@
         <v>7030</v>
       </c>
       <c r="BM75" t="n">
-        <v>0.2073648748874169</v>
+        <v>0.207364874887417</v>
       </c>
       <c r="BN75" t="n">
         <v>0</v>
@@ -21781,7 +21781,7 @@
         <v>6006</v>
       </c>
       <c r="BM94" t="n">
-        <v>0.4081434338136364</v>
+        <v>0.4081434338136363</v>
       </c>
       <c r="BN94" t="n">
         <v>0</v>
@@ -23991,7 +23991,7 @@
         <v>5002</v>
       </c>
       <c r="BM104" t="n">
-        <v>0.3203562291143765</v>
+        <v>0.3203562291143766</v>
       </c>
       <c r="BN104" t="n">
         <v>0</v>
@@ -24212,7 +24212,7 @@
         <v>5063</v>
       </c>
       <c r="BM105" t="n">
-        <v>0.3529848251567294</v>
+        <v>0.3529848251567295</v>
       </c>
       <c r="BN105" t="n">
         <v>0</v>
@@ -24875,7 +24875,7 @@
         <v>5865</v>
       </c>
       <c r="BM108" t="n">
-        <v>0.5539650626263636</v>
+        <v>0.5539650626263635</v>
       </c>
       <c r="BN108" t="n">
         <v>1</v>
@@ -26201,7 +26201,7 @@
         <v>6059</v>
       </c>
       <c r="BM114" t="n">
-        <v>0.3365267942486094</v>
+        <v>0.3365267942486093</v>
       </c>
       <c r="BN114" t="n">
         <v>0</v>
@@ -26422,7 +26422,7 @@
         <v>5428</v>
       </c>
       <c r="BM115" t="n">
-        <v>0.4878581549861446</v>
+        <v>0.4878581549861447</v>
       </c>
       <c r="BN115" t="n">
         <v>0</v>
@@ -29516,7 +29516,7 @@
         <v>3588</v>
       </c>
       <c r="BM129" t="n">
-        <v>0.4970639818663699</v>
+        <v>0.4970639818663697</v>
       </c>
       <c r="BN129" t="n">
         <v>0</v>
@@ -30621,7 +30621,7 @@
         <v>3036</v>
       </c>
       <c r="BM134" t="n">
-        <v>0.5803698588341547</v>
+        <v>0.5803698588341546</v>
       </c>
       <c r="BN134" t="n">
         <v>1</v>
@@ -31063,7 +31063,7 @@
         <v>2175</v>
       </c>
       <c r="BM136" t="n">
-        <v>0.4944872726831188</v>
+        <v>0.4944872726831187</v>
       </c>
       <c r="BN136" t="n">
         <v>0</v>
@@ -33715,7 +33715,7 @@
         <v>4876</v>
       </c>
       <c r="BM148" t="n">
-        <v>0.4435955916577572</v>
+        <v>0.443595591657757</v>
       </c>
       <c r="BN148" t="n">
         <v>0</v>
@@ -34157,7 +34157,7 @@
         <v>5005</v>
       </c>
       <c r="BM150" t="n">
-        <v>0.5082368708918693</v>
+        <v>0.5082368708918694</v>
       </c>
       <c r="BN150" t="n">
         <v>1</v>
@@ -34820,7 +34820,7 @@
         <v>4698</v>
       </c>
       <c r="BM153" t="n">
-        <v>0.5240110223822422</v>
+        <v>0.5240110223822423</v>
       </c>
       <c r="BN153" t="n">
         <v>1</v>
@@ -35041,7 +35041,7 @@
         <v>4752</v>
       </c>
       <c r="BM154" t="n">
-        <v>0.4938753612656604</v>
+        <v>0.4938753612656605</v>
       </c>
       <c r="BN154" t="n">
         <v>0</v>

--- a/Rodovias/modelos_rodovias/floriano_rodrigues_pinheiro_km_26_pindamonhangaba_sp_rf_regimes/predicoes_teste.xlsx
+++ b/Rodovias/modelos_rodovias/floriano_rodrigues_pinheiro_km_26_pindamonhangaba_sp_rf_regimes/predicoes_teste.xlsx
@@ -2809,7 +2809,7 @@
         <v>10586</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.3463319011348111</v>
+        <v>0.346331901134811</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>10112</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.283533952596522</v>
+        <v>0.2835339525965221</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>10902</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.3307986253456406</v>
+        <v>0.3307986253456405</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
         <v>11060</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.3290512787696764</v>
+        <v>0.3290512787696763</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
@@ -4870,7 +4870,7 @@
         <v>10507</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.3025164667501004</v>
+        <v>0.3025164667501005</v>
       </c>
       <c r="BN19" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>10981</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.3108895090262087</v>
+        <v>0.3108895090262086</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
         <v>8300</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.4081193437852535</v>
+        <v>0.4081193437852536</v>
       </c>
       <c r="BN25" t="n">
         <v>0</v>
@@ -8992,7 +8992,7 @@
         <v>5510</v>
       </c>
       <c r="BM37" t="n">
-        <v>0.7381640134663781</v>
+        <v>0.7381640134663779</v>
       </c>
       <c r="BN37" t="n">
         <v>1</v>
@@ -10137,7 +10137,7 @@
         <v>6460</v>
       </c>
       <c r="BM42" t="n">
-        <v>0.5438589918395283</v>
+        <v>0.5438589918395282</v>
       </c>
       <c r="BN42" t="n">
         <v>1</v>
@@ -10595,7 +10595,7 @@
         <v>7980</v>
       </c>
       <c r="BM44" t="n">
-        <v>0.3162672626947002</v>
+        <v>0.3162672626947003</v>
       </c>
       <c r="BN44" t="n">
         <v>0</v>
@@ -12198,7 +12198,7 @@
         <v>6014</v>
       </c>
       <c r="BM51" t="n">
-        <v>0.285653089984004</v>
+        <v>0.2856530899840041</v>
       </c>
       <c r="BN51" t="n">
         <v>0</v>
@@ -12885,7 +12885,7 @@
         <v>3724</v>
       </c>
       <c r="BM54" t="n">
-        <v>0.4208071598884751</v>
+        <v>0.4208071598884752</v>
       </c>
       <c r="BN54" t="n">
         <v>0</v>
@@ -13343,7 +13343,7 @@
         <v>3920</v>
       </c>
       <c r="BM56" t="n">
-        <v>0.3547142486085616</v>
+        <v>0.3547142486085617</v>
       </c>
       <c r="BN56" t="n">
         <v>0</v>
@@ -14030,7 +14030,7 @@
         <v>1666</v>
       </c>
       <c r="BM59" t="n">
-        <v>0.3718588245816427</v>
+        <v>0.3718588245816426</v>
       </c>
       <c r="BN59" t="n">
         <v>0</v>
@@ -14259,7 +14259,7 @@
         <v>2156</v>
       </c>
       <c r="BM60" t="n">
-        <v>0.499934562161569</v>
+        <v>0.4999345621615691</v>
       </c>
       <c r="BN60" t="n">
         <v>0</v>
@@ -16256,7 +16256,7 @@
         <v>4655</v>
       </c>
       <c r="BM69" t="n">
-        <v>0.6121966455859124</v>
+        <v>0.6121966455859125</v>
       </c>
       <c r="BN69" t="n">
         <v>1</v>
@@ -16698,7 +16698,7 @@
         <v>4940</v>
       </c>
       <c r="BM71" t="n">
-        <v>0.4656560493319477</v>
+        <v>0.4656560493319478</v>
       </c>
       <c r="BN71" t="n">
         <v>0</v>
@@ -16919,7 +16919,7 @@
         <v>5415</v>
       </c>
       <c r="BM72" t="n">
-        <v>0.2633445600914125</v>
+        <v>0.2633445600914126</v>
       </c>
       <c r="BN72" t="n">
         <v>0</v>
@@ -17582,7 +17582,7 @@
         <v>7030</v>
       </c>
       <c r="BM75" t="n">
-        <v>0.207364874887417</v>
+        <v>0.2073648748874169</v>
       </c>
       <c r="BN75" t="n">
         <v>0</v>
@@ -21781,7 +21781,7 @@
         <v>6006</v>
       </c>
       <c r="BM94" t="n">
-        <v>0.4081434338136363</v>
+        <v>0.4081434338136362</v>
       </c>
       <c r="BN94" t="n">
         <v>0</v>
@@ -22223,7 +22223,7 @@
         <v>6083</v>
       </c>
       <c r="BM96" t="n">
-        <v>0.4767024618349002</v>
+        <v>0.4767024618349001</v>
       </c>
       <c r="BN96" t="n">
         <v>0</v>
@@ -22444,7 +22444,7 @@
         <v>6241</v>
       </c>
       <c r="BM97" t="n">
-        <v>0.3641749446044067</v>
+        <v>0.3641749446044066</v>
       </c>
       <c r="BN97" t="n">
         <v>0</v>
@@ -23991,7 +23991,7 @@
         <v>5002</v>
       </c>
       <c r="BM104" t="n">
-        <v>0.3203562291143766</v>
+        <v>0.3203562291143765</v>
       </c>
       <c r="BN104" t="n">
         <v>0</v>
@@ -24875,7 +24875,7 @@
         <v>5865</v>
       </c>
       <c r="BM108" t="n">
-        <v>0.5539650626263635</v>
+        <v>0.5539650626263636</v>
       </c>
       <c r="BN108" t="n">
         <v>1</v>
@@ -27306,7 +27306,7 @@
         <v>5796</v>
       </c>
       <c r="BM119" t="n">
-        <v>0.3764061301496907</v>
+        <v>0.3764061301496906</v>
       </c>
       <c r="BN119" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>4512</v>
       </c>
       <c r="BM122" t="n">
-        <v>0.5972974261761597</v>
+        <v>0.5972974261761598</v>
       </c>
       <c r="BN122" t="n">
         <v>1</v>
@@ -29295,7 +29295,7 @@
         <v>3854</v>
       </c>
       <c r="BM128" t="n">
-        <v>0.5446465218518903</v>
+        <v>0.5446465218518902</v>
       </c>
       <c r="BN128" t="n">
         <v>1</v>
@@ -29516,7 +29516,7 @@
         <v>3588</v>
       </c>
       <c r="BM129" t="n">
-        <v>0.4970639818663697</v>
+        <v>0.4970639818663699</v>
       </c>
       <c r="BN129" t="n">
         <v>0</v>
@@ -30621,7 +30621,7 @@
         <v>3036</v>
       </c>
       <c r="BM134" t="n">
-        <v>0.5803698588341546</v>
+        <v>0.5803698588341547</v>
       </c>
       <c r="BN134" t="n">
         <v>1</v>
@@ -32168,7 +32168,7 @@
         <v>1672</v>
       </c>
       <c r="BM141" t="n">
-        <v>0.3869161484849244</v>
+        <v>0.3869161484849243</v>
       </c>
       <c r="BN141" t="n">
         <v>0</v>
@@ -33494,7 +33494,7 @@
         <v>4600</v>
       </c>
       <c r="BM147" t="n">
-        <v>0.7039792300425501</v>
+        <v>0.70397923004255</v>
       </c>
       <c r="BN147" t="n">
         <v>1</v>
@@ -33715,7 +33715,7 @@
         <v>4876</v>
       </c>
       <c r="BM148" t="n">
-        <v>0.443595591657757</v>
+        <v>0.4435955916577571</v>
       </c>
       <c r="BN148" t="n">
         <v>0</v>
@@ -34157,7 +34157,7 @@
         <v>5005</v>
       </c>
       <c r="BM150" t="n">
-        <v>0.5082368708918694</v>
+        <v>0.5082368708918693</v>
       </c>
       <c r="BN150" t="n">
         <v>1</v>
@@ -34820,7 +34820,7 @@
         <v>4698</v>
       </c>
       <c r="BM153" t="n">
-        <v>0.5240110223822423</v>
+        <v>0.5240110223822422</v>
       </c>
       <c r="BN153" t="n">
         <v>1</v>
@@ -35041,7 +35041,7 @@
         <v>4752</v>
       </c>
       <c r="BM154" t="n">
-        <v>0.4938753612656605</v>
+        <v>0.4938753612656604</v>
       </c>
       <c r="BN154" t="n">
         <v>0</v>
@@ -35262,7 +35262,7 @@
         <v>3816</v>
       </c>
       <c r="BM155" t="n">
-        <v>0.6681179925895531</v>
+        <v>0.668117992589553</v>
       </c>
       <c r="BN155" t="n">
         <v>1</v>

--- a/Rodovias/modelos_rodovias/floriano_rodrigues_pinheiro_km_26_pindamonhangaba_sp_rf_regimes/predicoes_teste.xlsx
+++ b/Rodovias/modelos_rodovias/floriano_rodrigues_pinheiro_km_26_pindamonhangaba_sp_rf_regimes/predicoes_teste.xlsx
@@ -4209,7 +4209,7 @@
         <v>10902</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.3149447529469575</v>
+        <v>0.3149447529469576</v>
       </c>
       <c r="BY14" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
         <v>12087</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.3564299177866916</v>
+        <v>0.3564299177866917</v>
       </c>
       <c r="BY17" t="n">
         <v>0</v>
@@ -5257,7 +5257,7 @@
         <v>11060</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.4634536564742027</v>
+        <v>0.4634536564742026</v>
       </c>
       <c r="BY18" t="n">
         <v>0</v>
@@ -6305,7 +6305,7 @@
         <v>11929</v>
       </c>
       <c r="BX22" t="n">
-        <v>0.3881733433668685</v>
+        <v>0.3881733433668686</v>
       </c>
       <c r="BY22" t="n">
         <v>0</v>
@@ -11283,7 +11283,7 @@
         <v>7410</v>
       </c>
       <c r="BX41" t="n">
-        <v>0.5773187062850922</v>
+        <v>0.5773187062850921</v>
       </c>
       <c r="BY41" t="n">
         <v>1</v>
@@ -15737,7 +15737,7 @@
         <v>1568</v>
       </c>
       <c r="BX58" t="n">
-        <v>0.3440884294286315</v>
+        <v>0.3440884294286316</v>
       </c>
       <c r="BY58" t="n">
         <v>0</v>
@@ -17539,7 +17539,7 @@
         <v>3007</v>
       </c>
       <c r="BX65" t="n">
-        <v>0.5099428090110245</v>
+        <v>0.5099428090110244</v>
       </c>
       <c r="BY65" t="n">
         <v>1</v>
@@ -19063,7 +19063,7 @@
         <v>4940</v>
       </c>
       <c r="BX71" t="n">
-        <v>0.5175816946692324</v>
+        <v>0.5175816946692325</v>
       </c>
       <c r="BY71" t="n">
         <v>1</v>
@@ -21603,7 +21603,7 @@
         <v>5670</v>
       </c>
       <c r="BX81" t="n">
-        <v>0.7302803187289548</v>
+        <v>0.7302803187289549</v>
       </c>
       <c r="BY81" t="n">
         <v>1</v>
@@ -22619,7 +22619,7 @@
         <v>7912</v>
       </c>
       <c r="BX85" t="n">
-        <v>0.3180634662166184</v>
+        <v>0.3180634662166185</v>
       </c>
       <c r="BY85" t="n">
         <v>0</v>
@@ -23127,7 +23127,7 @@
         <v>6622</v>
       </c>
       <c r="BX87" t="n">
-        <v>0.5480864372456278</v>
+        <v>0.5480864372456277</v>
       </c>
       <c r="BY87" t="n">
         <v>1</v>
@@ -23381,7 +23381,7 @@
         <v>7238</v>
       </c>
       <c r="BX88" t="n">
-        <v>0.3084587074600257</v>
+        <v>0.3084587074600256</v>
       </c>
       <c r="BY88" t="n">
         <v>0</v>
@@ -26683,7 +26683,7 @@
         <v>4697</v>
       </c>
       <c r="BX101" t="n">
-        <v>0.4680704370762775</v>
+        <v>0.4680704370762777</v>
       </c>
       <c r="BY101" t="n">
         <v>0</v>
@@ -28715,7 +28715,7 @@
         <v>5621</v>
       </c>
       <c r="BX109" t="n">
-        <v>0.6900019841433617</v>
+        <v>0.6900019841433618</v>
       </c>
       <c r="BY109" t="n">
         <v>1</v>
@@ -29477,7 +29477,7 @@
         <v>6142</v>
       </c>
       <c r="BX112" t="n">
-        <v>0.7120221017551907</v>
+        <v>0.7120221017551908</v>
       </c>
       <c r="BY112" t="n">
         <v>1</v>
@@ -29731,7 +29731,7 @@
         <v>6142</v>
       </c>
       <c r="BX113" t="n">
-        <v>0.3231301001406001</v>
+        <v>0.3231301001406</v>
       </c>
       <c r="BY113" t="n">
         <v>0</v>
@@ -32779,7 +32779,7 @@
         <v>4700</v>
       </c>
       <c r="BX125" t="n">
-        <v>0.5053662737019819</v>
+        <v>0.5053662737019818</v>
       </c>
       <c r="BY125" t="n">
         <v>1</v>
@@ -33033,7 +33033,7 @@
         <v>3478</v>
       </c>
       <c r="BX126" t="n">
-        <v>0.4538325760179566</v>
+        <v>0.4538325760179565</v>
       </c>
       <c r="BY126" t="n">
         <v>0</v>
@@ -34557,7 +34557,7 @@
         <v>1656</v>
       </c>
       <c r="BX132" t="n">
-        <v>0.3928159366630523</v>
+        <v>0.3928159366630522</v>
       </c>
       <c r="BY132" t="n">
         <v>0</v>
@@ -35319,7 +35319,7 @@
         <v>1827</v>
       </c>
       <c r="BX135" t="n">
-        <v>0.5118905454967659</v>
+        <v>0.511890545496766</v>
       </c>
       <c r="BY135" t="n">
         <v>1</v>
@@ -36589,7 +36589,7 @@
         <v>1827</v>
       </c>
       <c r="BX140" t="n">
-        <v>0.337533207965064</v>
+        <v>0.3375332079650639</v>
       </c>
       <c r="BY140" t="n">
         <v>0</v>
@@ -37097,7 +37097,7 @@
         <v>1710</v>
       </c>
       <c r="BX142" t="n">
-        <v>0.6591497707737514</v>
+        <v>0.6591497707737515</v>
       </c>
       <c r="BY142" t="n">
         <v>1</v>
@@ -38621,7 +38621,7 @@
         <v>4876</v>
       </c>
       <c r="BX148" t="n">
-        <v>0.4566586398066728</v>
+        <v>0.4566586398066729</v>
       </c>
       <c r="BY148" t="n">
         <v>0</v>
@@ -40399,7 +40399,7 @@
         <v>3816</v>
       </c>
       <c r="BX155" t="n">
-        <v>0.5448506709430947</v>
+        <v>0.5448506709430949</v>
       </c>
       <c r="BY155" t="n">
         <v>1</v>
@@ -40653,7 +40653,7 @@
         <v>2376</v>
       </c>
       <c r="BX156" t="n">
-        <v>0.625686097516871</v>
+        <v>0.6256860975168711</v>
       </c>
       <c r="BY156" t="n">
         <v>1</v>
